--- a/test/excel/xlsx/saved/arrays-5.xlsx
+++ b/test/excel/xlsx/saved/arrays-5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11004"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26256D37-E4D2-A343-9F00-56AA824DFE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1895FE6F-01B9-8A45-8AE5-0490C7C8B484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,6 +216,18 @@
     <t>1,5</t>
   </si>
   <si>
+    <t>lift:IPMT#1</t>
+  </si>
+  <si>
+    <t>lift:IPMT#2</t>
+  </si>
+  <si>
+    <t>lift:IPMT#3</t>
+  </si>
+  <si>
+    <t>lift:IPMT#4</t>
+  </si>
+  <si>
     <t>lift:IPMT#5</t>
   </si>
   <si>
@@ -1402,18 +1414,6 @@
   </si>
   <si>
     <t>lift:PRICE#6</t>
-  </si>
-  <si>
-    <t>lift:PRICE#7</t>
-  </si>
-  <si>
-    <t>lift:PRICE#8</t>
-  </si>
-  <si>
-    <t>lift:PRICE#9</t>
-  </si>
-  <si>
-    <t>lift:PRICE#10</t>
   </si>
   <si>
     <t>end</t>
@@ -3047,7 +3047,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A1" ca="1">IPMT(0.00833333333333333,1,D!B1:B2,8000)</f>
+        <f t="array" aca="1" ref="A1" ca="1">IPMT(D!B1:B2,1,36,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B1">
@@ -3068,7 +3068,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A2" ca="1">IPMT(0.00833333333333333,1,{1;2},8000)</f>
+        <f t="array" aca="1" ref="A2" ca="1">IPMT({1;2},1,36,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2">
@@ -3089,7 +3089,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A3" ca="1">IPMT(0.00833333333333333,1,36,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A3" ca="1">IPMT(0.00833333333333333,D!B1:B2,36,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B3">
@@ -3110,7 +3110,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A4" ca="1">IPMT(0.00833333333333333,1,36,{1;2})</f>
+        <f t="array" aca="1" ref="A4" ca="1">IPMT(0.00833333333333333,{1;2},36,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B4">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A5" ca="1">ISBLANK(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A5" ca="1">IPMT(0.00833333333333333,1,D!B1:B2,8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B5">
@@ -3152,7 +3152,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A6" ca="1">ISBLANK({1;2})</f>
+        <f t="array" aca="1" ref="A6" ca="1">IPMT(0.00833333333333333,1,{1;2},8000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6">
@@ -3173,7 +3173,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A7" ca="1">ISERR(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A7" ca="1">IPMT(0.00833333333333333,1,36,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B7">
@@ -3194,7 +3194,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A8" ca="1">ISERR({1;2})</f>
+        <f t="array" aca="1" ref="A8" ca="1">IPMT(0.00833333333333333,1,36,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B8">
@@ -3215,7 +3215,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A9" ca="1">ISERROR(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A9" ca="1">ISBLANK(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B9">
@@ -3236,7 +3236,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A10" ca="1">ISERROR({1;2})</f>
+        <f t="array" aca="1" ref="A10" ca="1">ISBLANK({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B10">
@@ -3256,104 +3256,104 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="e" cm="1">
-        <f t="array" ref="A11">ISEVEN(D!B1:B2)</f>
+      <c r="A11" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A11" ca="1">ISERR(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B11">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A12" ca="1">ISERR({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A13" ca="1">ISERROR(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A14" ca="1">ISERROR({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B14">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="e" cm="1">
+        <f t="array" ref="A15">ISEVEN(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C11">
+      <c r="C15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A12" ca="1">ISEVEN({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B12">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A13" ca="1">ISLOGICAL(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B13">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A14" ca="1">ISLOGICAL({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B14">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C14">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D14" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A15" ca="1">ISNA(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B15">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C15">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D15" t="str">
-        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E15" t="s">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A16" ca="1">ISNA({1;2})</f>
+        <f t="array" aca="1" ref="A16" ca="1">ISEVEN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B16">
@@ -3383,7 +3383,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A17" ca="1">ISNONTEXT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A17" ca="1">ISLOGICAL(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B17">
@@ -3404,7 +3404,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A18" ca="1">ISNONTEXT({1;2})</f>
+        <f t="array" aca="1" ref="A18" ca="1">ISLOGICAL({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B18">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A19" ca="1">ISNUMBER(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A19" ca="1">ISNA(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B19">
@@ -3446,7 +3446,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A20" ca="1">ISNUMBER({1;2})</f>
+        <f t="array" aca="1" ref="A20" ca="1">ISNA({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B20">
@@ -3467,7 +3467,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A21" ca="1">ISO.CEILING(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A21" ca="1">ISNONTEXT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B21">
@@ -3488,7 +3488,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A22" ca="1">ISO.CEILING({1;2})</f>
+        <f t="array" aca="1" ref="A22" ca="1">ISNONTEXT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B22">
@@ -3508,104 +3508,104 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="e" cm="1">
-        <f t="array" ref="A23">ISODD(D!B1:B2)</f>
+      <c r="A23" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A23" ca="1">ISNUMBER(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B23">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A24" ca="1">ISNUMBER({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A25" ca="1">ISO.CEILING(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A26" ca="1">ISO.CEILING({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="e" cm="1">
+        <f t="array" ref="A27">ISODD(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C23">
+      <c r="C27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D27" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A24" ca="1">ISODD({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B24">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C24">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D24" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A25" ca="1">_xlfn.ISOWEEKNUM(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B25">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C25">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A26" ca="1">_xlfn.ISOWEEKNUM({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B26">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C26">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D26" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A27" ca="1">ISPMT(D!B1:B2,1,36,8000000)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B27">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C27">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D27" t="str">
-        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E27" t="s">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A28" ca="1">ISPMT({1;2},1,36,8000000)</f>
+        <f t="array" aca="1" ref="A28" ca="1">ISODD({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B28">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A29" ca="1">ISPMT(0.00833333333333333,D!B1:B2,36,8000000)</f>
+        <f t="array" aca="1" ref="A29" ca="1">_xlfn.ISOWEEKNUM(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B29">
@@ -3656,7 +3656,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A30" ca="1">ISPMT(0.00833333333333333,{1;2},36,8000000)</f>
+        <f t="array" aca="1" ref="A30" ca="1">_xlfn.ISOWEEKNUM({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B30">
@@ -3677,7 +3677,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A31" ca="1">ISPMT(0.00833333333333333,1,D!B1:B2,8000000)</f>
+        <f t="array" aca="1" ref="A31" ca="1">ISPMT(D!B1:B2,1,36,8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B31">
@@ -3698,7 +3698,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A32" ca="1">ISPMT(0.00833333333333333,1,{1;2},8000000)</f>
+        <f t="array" aca="1" ref="A32" ca="1">ISPMT({1;2},1,36,8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B32">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A33" ca="1">ISPMT(0.00833333333333333,1,36,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A33" ca="1">ISPMT(0.00833333333333333,D!B1:B2,36,8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B33">
@@ -3740,7 +3740,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A34" ca="1">ISPMT(0.00833333333333333,1,36,{1;2})</f>
+        <f t="array" aca="1" ref="A34" ca="1">ISPMT(0.00833333333333333,{1;2},36,8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B34">
@@ -3761,7 +3761,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A35" ca="1">ISTEXT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A35" ca="1">ISPMT(0.00833333333333333,1,D!B1:B2,8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B35">
@@ -3782,7 +3782,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A36" ca="1">ISTEXT({1;2})</f>
+        <f t="array" aca="1" ref="A36" ca="1">ISPMT(0.00833333333333333,1,{1;2},8000000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B36">
@@ -3803,7 +3803,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A37" ca="1">LARGE(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A37" ca="1">ISPMT(0.00833333333333333,1,36,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B37">
@@ -3824,7 +3824,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A38" ca="1">LARGE(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A38" ca="1">ISPMT(0.00833333333333333,1,36,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B38">
@@ -3844,167 +3844,167 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" cm="1">
-        <f t="array" ref="A39">LCM(D!B1:B2,2)</f>
+      <c r="A39" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A39" ca="1">ISTEXT(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B39">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A40" ca="1">ISTEXT({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A41" ca="1">LARGE(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B41">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A42" ca="1">LARGE(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" cm="1">
+        <f t="array" ref="A43">LCM(D!B1:B2,2)</f>
         <v>8</v>
       </c>
-      <c r="B39">
+      <c r="B43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C39">
+      <c r="C43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D43" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" cm="1">
-        <f t="array" ref="A40">LCM({1;2},2)</f>
+      <c r="E43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" cm="1">
+        <f t="array" ref="A44">LCM({1;2},2)</f>
         <v>2</v>
       </c>
-      <c r="B40">
+      <c r="B44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C44">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D44" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E40" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" cm="1">
-        <f t="array" ref="A41">LCM(5,D!B1:B2)</f>
+      <c r="E44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" cm="1">
+        <f t="array" ref="A45">LCM(5,D!B1:B2)</f>
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C41">
+      <c r="C45">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D45" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" cm="1">
-        <f t="array" ref="A42">LCM(5,{1;2})</f>
+      <c r="E45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" cm="1">
+        <f t="array" ref="A46">LCM(5,{1;2})</f>
         <v>10</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C42">
+      <c r="C46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D46" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A43" ca="1">LEFT(D!B1:B2,4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B43">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C43">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D43" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A44" ca="1">LEFT({1;2},4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B44">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C44">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D44" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A45" ca="1">LEFT("Sale Price",D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B45">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C45">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D45" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="E45" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A46" ca="1">LEFT("Sale Price",{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B46">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D46" t="str">
-        <f t="shared" ca="1" si="2"/>
         <v/>
       </c>
       <c r="E46" t="s">
@@ -4013,7 +4013,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A47" ca="1">LEFTB(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A47" ca="1">LEFT(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B47">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A48" ca="1">LEFTB({1;2},2)</f>
+        <f t="array" aca="1" ref="A48" ca="1">LEFT({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B48">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A49" ca="1">LEFTB("abc",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A49" ca="1">LEFT("Sale Price",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B49">
@@ -4076,7 +4076,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A50" ca="1">LEFTB("abc",{1;2})</f>
+        <f t="array" aca="1" ref="A50" ca="1">LEFT("Sale Price",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B50">
@@ -4097,7 +4097,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A51" ca="1">LEN(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A51" ca="1">LEFTB(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B51">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A52" ca="1">LEN({1;2})</f>
+        <f t="array" aca="1" ref="A52" ca="1">LEFTB({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B52">
@@ -4139,7 +4139,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A53" ca="1">LENB(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A53" ca="1">LEFTB("abc",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B53">
@@ -4160,7 +4160,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A54" ca="1">LENB({1;2})</f>
+        <f t="array" aca="1" ref="A54" ca="1">LEFTB("abc",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B54">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A55" ca="1">LN(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A55" ca="1">LEN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B55">
@@ -4202,7 +4202,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A56" ca="1">LN({1;2})</f>
+        <f t="array" aca="1" ref="A56" ca="1">LEN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B56">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A57" ca="1">LOG(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A57" ca="1">LENB(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B57">
@@ -4244,7 +4244,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A58" ca="1">LOG({1;2})</f>
+        <f t="array" aca="1" ref="A58" ca="1">LENB({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B58">
@@ -4265,7 +4265,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A59" ca="1">LOG10(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A59" ca="1">LN(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B59">
@@ -4286,7 +4286,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A60" ca="1">LOG10({1;2})</f>
+        <f t="array" aca="1" ref="A60" ca="1">LN({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B60">
@@ -4307,7 +4307,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A61" ca="1">LOGINV(D!B1:B2,3.5,1.2)</f>
+        <f t="array" aca="1" ref="A61" ca="1">LOG(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B61">
@@ -4328,7 +4328,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A62" ca="1">LOGINV({1;2},3.5,1.2)</f>
+        <f t="array" aca="1" ref="A62" ca="1">LOG({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B62">
@@ -4349,7 +4349,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A63" ca="1">LOGINV(0.039084,D!B1:B2,1.2)</f>
+        <f t="array" aca="1" ref="A63" ca="1">LOG10(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B63">
@@ -4370,7 +4370,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A64" ca="1">LOGINV(0.039084,{1;2},1.2)</f>
+        <f t="array" aca="1" ref="A64" ca="1">LOG10({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B64">
@@ -4391,7 +4391,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A65" ca="1">LOGINV(0.039084,3.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A65" ca="1">LOGINV(D!B1:B2,3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B65">
@@ -4412,7 +4412,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A66" ca="1">LOGINV(0.039084,3.5,{1;2})</f>
+        <f t="array" aca="1" ref="A66" ca="1">LOGINV({1;2},3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B66">
@@ -4433,7 +4433,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A67" ca="1">_xlfn.LOGNORM.DIST(D!B1:B2,3.5,1.2,TRUE)</f>
+        <f t="array" aca="1" ref="A67" ca="1">LOGINV(0.039084,D!B1:B2,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B67">
@@ -4454,7 +4454,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A68" ca="1">_xlfn.LOGNORM.DIST({1;2},3.5,1.2,TRUE)</f>
+        <f t="array" aca="1" ref="A68" ca="1">LOGINV(0.039084,{1;2},1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B68">
@@ -4475,7 +4475,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A69" ca="1">_xlfn.LOGNORM.DIST(4,D!B1:B2,1.2,TRUE)</f>
+        <f t="array" aca="1" ref="A69" ca="1">LOGINV(0.039084,3.5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B69">
@@ -4496,7 +4496,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A70" ca="1">_xlfn.LOGNORM.DIST(4,{1;2},1.2,TRUE)</f>
+        <f t="array" aca="1" ref="A70" ca="1">LOGINV(0.039084,3.5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B70">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A71" ca="1">_xlfn.LOGNORM.DIST(4,3.5,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A71" ca="1">_xlfn.LOGNORM.DIST(D!B1:B2,3.5,1.2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B71">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A72" ca="1">_xlfn.LOGNORM.DIST(4,3.5,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A72" ca="1">_xlfn.LOGNORM.DIST({1;2},3.5,1.2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B72">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A73" ca="1">_xlfn.LOGNORM.DIST(4,3.5,1.2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A73" ca="1">_xlfn.LOGNORM.DIST(4,D!B1:B2,1.2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B73">
@@ -4580,7 +4580,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A74" ca="1">_xlfn.LOGNORM.DIST(4,3.5,1.2,{1;2})</f>
+        <f t="array" aca="1" ref="A74" ca="1">_xlfn.LOGNORM.DIST(4,{1;2},1.2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B74">
@@ -4601,7 +4601,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A75" ca="1">_xlfn.LOGNORM.INV(D!B1:B2,3.5,1.2)</f>
+        <f t="array" aca="1" ref="A75" ca="1">_xlfn.LOGNORM.DIST(4,3.5,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B75">
@@ -4622,7 +4622,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A76" ca="1">_xlfn.LOGNORM.INV({1;2},3.5,1.2)</f>
+        <f t="array" aca="1" ref="A76" ca="1">_xlfn.LOGNORM.DIST(4,3.5,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B76">
@@ -4643,7 +4643,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A77" ca="1">_xlfn.LOGNORM.INV(0.039084,D!B1:B2,1.2)</f>
+        <f t="array" aca="1" ref="A77" ca="1">_xlfn.LOGNORM.DIST(4,3.5,1.2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B77">
@@ -4664,7 +4664,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A78" ca="1">_xlfn.LOGNORM.INV(0.039084,{1;2},1.2)</f>
+        <f t="array" aca="1" ref="A78" ca="1">_xlfn.LOGNORM.DIST(4,3.5,1.2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B78">
@@ -4685,7 +4685,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A79" ca="1">_xlfn.LOGNORM.INV(0.039084,3.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A79" ca="1">_xlfn.LOGNORM.INV(D!B1:B2,3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B79">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A80" ca="1">_xlfn.LOGNORM.INV(0.039084,3.5,{1;2})</f>
+        <f t="array" aca="1" ref="A80" ca="1">_xlfn.LOGNORM.INV({1;2},3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B80">
@@ -4727,7 +4727,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A81" ca="1">LOGNORMDIST(D!B1:B2,3.5,1.2)</f>
+        <f t="array" aca="1" ref="A81" ca="1">_xlfn.LOGNORM.INV(0.039084,D!B1:B2,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B81">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A82" ca="1">LOGNORMDIST({1;2},3.5,1.2)</f>
+        <f t="array" aca="1" ref="A82" ca="1">_xlfn.LOGNORM.INV(0.039084,{1;2},1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B82">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A83" ca="1">LOGNORMDIST(4,D!B1:B2,1.2)</f>
+        <f t="array" aca="1" ref="A83" ca="1">_xlfn.LOGNORM.INV(0.039084,3.5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B83">
@@ -4790,7 +4790,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A84" ca="1">LOGNORMDIST(4,{1;2},1.2)</f>
+        <f t="array" aca="1" ref="A84" ca="1">_xlfn.LOGNORM.INV(0.039084,3.5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B84">
@@ -4811,7 +4811,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A85" ca="1">LOGNORMDIST(4,3.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A85" ca="1">LOGNORMDIST(D!B1:B2,3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B85">
@@ -4832,7 +4832,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A86" ca="1">LOGNORMDIST(4,3.5,{1;2})</f>
+        <f t="array" aca="1" ref="A86" ca="1">LOGNORMDIST({1;2},3.5,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B86">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A87" ca="1">LOOKUP(D!B1:B2,D!L1:L6,D!N1:N6)</f>
+        <f t="array" aca="1" ref="A87" ca="1">LOGNORMDIST(4,D!B1:B2,1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B87">
@@ -4874,7 +4874,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A88" ca="1">LOOKUP({1;2},D!L1:L6,D!N1:N6)</f>
+        <f t="array" aca="1" ref="A88" ca="1">LOGNORMDIST(4,{1;2},1.2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B88">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A89" ca="1">LOWER(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A89" ca="1">LOGNORMDIST(4,3.5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B89">
@@ -4916,7 +4916,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A90" ca="1">LOWER({1;2})</f>
+        <f t="array" aca="1" ref="A90" ca="1">LOGNORMDIST(4,3.5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B90">
@@ -4937,7 +4937,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A91" ca="1">MATCH(D!B1:B2,D!L1:L6,0)</f>
+        <f t="array" aca="1" ref="A91" ca="1">LOOKUP(D!B1:B2,D!L1:L6,D!N1:N6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B91">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A92" ca="1">MATCH({1;2},D!L1:L6,0)</f>
+        <f t="array" aca="1" ref="A92" ca="1">LOOKUP({1;2},D!L1:L6,D!N1:N6)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B92">
@@ -4978,102 +4978,102 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" cm="1">
-        <f t="array" ref="A93">MATCH(5,D!L1:L6,D!B1:B2)</f>
+      <c r="A93" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A93" ca="1">LOWER(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B93">
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="E93" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A94" ca="1">LOWER({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B94">
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C94">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="E94" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A95" ca="1">MATCH(D!B1:B2,D!L1:L6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B95">
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C95">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="E95" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A96" ca="1">MATCH({1;2},D!L1:L6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B96">
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="E96" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" cm="1">
+        <f t="array" ref="A97">MATCH(5,D!L1:L6,D!B1:B2)</f>
         <v>4</v>
       </c>
-      <c r="B93">
+      <c r="B97">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="C93">
+      <c r="C97">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="D93" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="E93" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A94" ca="1">MATCH(5,D!L1:L6,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B94">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="C94">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D94" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="E94" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A95" ca="1">_xlfn.MAXIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B95">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="C95">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D95" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="E95" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A96" ca="1">_xlfn.MAXIFS(D!G1:G7,D!G1:G7,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B96">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="C96">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D96" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="E96" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" t="e" cm="1">
-        <f t="array" ref="A97">MDURATION(D!B1:B2,DATE(2048,1,1),0.08,0.09,2,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B97">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="C97">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="D97" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A98" ca="1">MDURATION({1;2},DATE(2048,1,1),0.08,0.09,2,1)</f>
+        <f t="array" aca="1" ref="A98" ca="1">MATCH(5,D!L1:L6,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B98">
@@ -5104,20 +5104,20 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" t="e" cm="1">
-        <f t="array" ref="A99">MDURATION(DATE(2018,7,1),D!B1:B2,0.08,0.09,2,1)</f>
+      <c r="A99" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A99" ca="1">_xlfn.MAXIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B99">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
       </c>
       <c r="C99">
-        <f t="shared" si="4"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="D99" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="E99" t="s">
@@ -5126,7 +5126,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A100" ca="1">MDURATION(DATE(2018,7,1),{1;2},0.08,0.09,2,1)</f>
+        <f t="array" aca="1" ref="A100" ca="1">_xlfn.MAXIFS(D!G1:G7,D!G1:G7,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B100">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="e" cm="1">
-        <f t="array" ref="A101">MDURATION(DATE(2018,7,1),DATE(2048,1,1),D!B1:B2,0.09,2,1)</f>
+        <f t="array" ref="A101">MDURATION(D!B1:B2,DATE(2048,1,1),0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B101">
@@ -5168,7 +5168,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A102" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),{1;2},0.09,2,1)</f>
+        <f t="array" aca="1" ref="A102" ca="1">MDURATION({1;2},DATE(2048,1,1),0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B102">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="e" cm="1">
-        <f t="array" ref="A103">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,D!B1:B2,2,1)</f>
+        <f t="array" ref="A103">MDURATION(DATE(2018,7,1),D!B1:B2,0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B103">
@@ -5210,7 +5210,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A104" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,{1;2},2,1)</f>
+        <f t="array" aca="1" ref="A104" ca="1">MDURATION(DATE(2018,7,1),{1;2},0.08,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B104">
@@ -5231,7 +5231,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="e" cm="1">
-        <f t="array" ref="A105">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,D!B1:B2,1)</f>
+        <f t="array" ref="A105">MDURATION(DATE(2018,7,1),DATE(2048,1,1),D!B1:B2,0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B105">
@@ -5252,7 +5252,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A106" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,{1;2},1)</f>
+        <f t="array" aca="1" ref="A106" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),{1;2},0.09,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B106">
@@ -5273,7 +5273,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="e" cm="1">
-        <f t="array" ref="A107">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,D!B1:B2)</f>
+        <f t="array" ref="A107">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,D!B1:B2,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B107">
@@ -5294,7 +5294,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A108" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,{1;2})</f>
+        <f t="array" aca="1" ref="A108" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,{1;2},2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B108">
@@ -5314,20 +5314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A109" ca="1">MID(D!B1:B2,1,5)</f>
+      <c r="A109" t="e" cm="1">
+        <f t="array" ref="A109">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B109">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C109">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D109" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E109" t="s">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A110" ca="1">MID({1;2},1,5)</f>
+        <f t="array" aca="1" ref="A110" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B110">
@@ -5356,20 +5356,20 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A111" ca="1">MID("Fluid Flow",D!B1:B2,5)</f>
+      <c r="A111" t="e" cm="1">
+        <f t="array" ref="A111">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B111">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="C111">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D111" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="E111" t="s">
@@ -5378,7 +5378,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A112" ca="1">MID("Fluid Flow",{1;2},5)</f>
+        <f t="array" aca="1" ref="A112" ca="1">MDURATION(DATE(2018,7,1),DATE(2048,1,1),0.08,0.09,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B112">
@@ -5399,7 +5399,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A113" ca="1">MID("Fluid Flow",1,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A113" ca="1">MID(D!B1:B2,1,5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B113">
@@ -5420,7 +5420,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A114" ca="1">MID("Fluid Flow",1,{1;2})</f>
+        <f t="array" aca="1" ref="A114" ca="1">MID({1;2},1,5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B114">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A115" ca="1">MIDB(D!B1:B2,2,3)</f>
+        <f t="array" aca="1" ref="A115" ca="1">MID("Fluid Flow",D!B1:B2,5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B115">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A116" ca="1">MIDB({1;2},2,3)</f>
+        <f t="array" aca="1" ref="A116" ca="1">MID("Fluid Flow",{1;2},5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B116">
@@ -5483,7 +5483,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A117" ca="1">MIDB("abcdef",D!B1:B2,3)</f>
+        <f t="array" aca="1" ref="A117" ca="1">MID("Fluid Flow",1,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B117">
@@ -5504,7 +5504,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A118" ca="1">MIDB("abcdef",{1;2},3)</f>
+        <f t="array" aca="1" ref="A118" ca="1">MID("Fluid Flow",1,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B118">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A119" ca="1">MIDB("abcdef",2,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A119" ca="1">MIDB(D!B1:B2,2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B119">
@@ -5546,7 +5546,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A120" ca="1">MIDB("abcdef",2,{1;2})</f>
+        <f t="array" aca="1" ref="A120" ca="1">MIDB({1;2},2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B120">
@@ -5567,7 +5567,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A121" ca="1">_xlfn.MINIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A121" ca="1">MIDB("abcdef",D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B121">
@@ -5588,7 +5588,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A122" ca="1">_xlfn.MINIFS(D!G1:G7,D!G1:G7,{1;2})</f>
+        <f t="array" aca="1" ref="A122" ca="1">MIDB("abcdef",{1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B122">
@@ -5609,7 +5609,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A123" ca="1">MINUTE(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A123" ca="1">MIDB("abcdef",2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B123">
@@ -5630,7 +5630,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A124" ca="1">MINUTE({1;2})</f>
+        <f t="array" aca="1" ref="A124" ca="1">MIDB("abcdef",2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B124">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A125" ca="1">MIRR(D!I1:I5,D!B1:B2,0.12)</f>
+        <f t="array" aca="1" ref="A125" ca="1">_xlfn.MINIFS(D!G1:G7,D!G1:G7,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B125">
@@ -5672,7 +5672,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A126" ca="1">MIRR(D!I1:I5,{1;2},0.12)</f>
+        <f t="array" aca="1" ref="A126" ca="1">_xlfn.MINIFS(D!G1:G7,D!G1:G7,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B126">
@@ -5693,7 +5693,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A127" ca="1">MIRR(D!I1:I5,0.1,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A127" ca="1">MINUTE(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B127">
@@ -5714,7 +5714,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A128" ca="1">MIRR(D!I1:I5,0.1,{1;2})</f>
+        <f t="array" aca="1" ref="A128" ca="1">MINUTE({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B128">
@@ -5735,7 +5735,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A129" ca="1">MOD(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A129" ca="1">MIRR(D!I1:I5,D!B1:B2,0.12)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B129">
@@ -5756,7 +5756,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A130" ca="1">MOD({1;2},2)</f>
+        <f t="array" aca="1" ref="A130" ca="1">MIRR(D!I1:I5,{1;2},0.12)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B130">
@@ -5777,7 +5777,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A131" ca="1">MOD(3,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A131" ca="1">MIRR(D!I1:I5,0.1,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B131">
@@ -5798,7 +5798,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A132" ca="1">MOD(3,{1;2})</f>
+        <f t="array" aca="1" ref="A132" ca="1">MIRR(D!I1:I5,0.1,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B132">
@@ -5818,482 +5818,482 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" cm="1">
-        <f t="array" ref="A133">MODE(D!B1:B2,2,2)</f>
+      <c r="A133" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A133" ca="1">MOD(D!B1:B2,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B133">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C133">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E133" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A134" ca="1">MOD({1;2},2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B134">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C134">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E134" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A135" ca="1">MOD(3,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B135">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C135">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E135" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A136" ca="1">MOD(3,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B136">
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C136">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="D136" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="E136" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" cm="1">
+        <f t="array" ref="A137">MODE(D!B1:B2,2,2)</f>
         <v>2</v>
       </c>
-      <c r="B133">
+      <c r="B137">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C133">
+      <c r="C137">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="D133" t="str">
+      <c r="D137" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E133" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" cm="1">
-        <f t="array" ref="A134">MODE({1;2},2,2)</f>
+      <c r="E137" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" cm="1">
+        <f t="array" ref="A138">MODE({1;2},2,2)</f>
         <v>2</v>
       </c>
-      <c r="B134">
+      <c r="B138">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C134">
+      <c r="C138">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="D134" t="str">
+      <c r="D138" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E134" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" t="e" cm="1">
-        <f t="array" ref="A135">MODE(1,D!B1:B2,2)</f>
+      <c r="E138" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" t="e" cm="1">
+        <f t="array" ref="A139">MODE(1,D!B1:B2,2)</f>
         <v>#N/A</v>
       </c>
-      <c r="B135">
+      <c r="B139">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C135">
+      <c r="C139">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D135" t="str">
+      <c r="D139" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E135" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" cm="1">
-        <f t="array" ref="A136">MODE(1,{1;2},2)</f>
+      <c r="E139" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" cm="1">
+        <f t="array" ref="A140">MODE(1,{1;2},2)</f>
         <v>1</v>
       </c>
-      <c r="B136">
+      <c r="B140">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C136">
+      <c r="C140">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="D136" t="str">
+      <c r="D140" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E136" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A137" t="e" cm="1">
-        <f t="array" ref="A137">MODE(1,2,D!B1:B2)</f>
+      <c r="E140" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" t="e" cm="1">
+        <f t="array" ref="A141">MODE(1,2,D!B1:B2)</f>
         <v>#N/A</v>
       </c>
-      <c r="B137">
+      <c r="B141">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C137">
+      <c r="C141">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D137" t="str">
+      <c r="D141" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E137" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" cm="1">
-        <f t="array" ref="A138">MODE(1,2,{1;2})</f>
+      <c r="E141" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" cm="1">
+        <f t="array" ref="A142">MODE(1,2,{1;2})</f>
         <v>1</v>
       </c>
-      <c r="B138">
+      <c r="B142">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C138">
+      <c r="C142">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="D138" t="str">
+      <c r="D142" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E138" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A139" ca="1">MONTH(D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B139">
+      <c r="E142" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A143" ca="1">MONTH(D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B143">
         <f t="shared" ca="1" si="6"/>
         <v>9</v>
       </c>
-      <c r="C139">
+      <c r="C143">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
-      <c r="D139" t="str">
+      <c r="D143" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
-      <c r="E139" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A140" ca="1">MONTH({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B140">
+      <c r="E143" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A144" ca="1">MONTH({1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B144">
         <f t="shared" ca="1" si="6"/>
         <v>9</v>
       </c>
-      <c r="C140">
+      <c r="C144">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
-      <c r="D140" t="str">
+      <c r="D144" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
-      <c r="E140" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" t="e" cm="1">
-        <f t="array" ref="A141">MROUND(D!B1:B2,3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B141">
+      <c r="E144" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" t="e" cm="1">
+        <f t="array" ref="A145">MROUND(D!B1:B2,3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B145">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="C141">
+      <c r="C145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D141" t="str">
+      <c r="D145" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E141" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A142" ca="1">MROUND({1;2},3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B142">
+      <c r="E145" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A146" ca="1">MROUND({1;2},3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B146">
         <f t="shared" ca="1" si="6"/>
         <v>9</v>
       </c>
-      <c r="C142">
+      <c r="C146">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
-      <c r="D142" t="str">
+      <c r="D146" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
-      <c r="E142" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" t="e" cm="1">
-        <f t="array" ref="A143">MROUND(10,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B143">
+      <c r="E146" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" t="e" cm="1">
+        <f t="array" ref="A147">MROUND(10,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B147">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="C143">
+      <c r="C147">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D143" t="str">
+      <c r="D147" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E143" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A144" ca="1">MROUND(10,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B144">
+      <c r="E147" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A148" ca="1">MROUND(10,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B148">
         <f t="shared" ca="1" si="6"/>
         <v>9</v>
       </c>
-      <c r="C144">
+      <c r="C148">
         <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
-      <c r="D144" t="str">
+      <c r="D148" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
-      <c r="E144" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145" cm="1">
-        <f t="array" ref="A145">MULTINOMIAL(D!B1:B2,3,4)</f>
+      <c r="E148" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" cm="1">
+        <f t="array" ref="A149">MULTINOMIAL(D!B1:B2,3,4)</f>
         <v>872972099.9999994</v>
       </c>
-      <c r="B145">
+      <c r="B149">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C145">
+      <c r="C149">
         <f t="shared" si="7"/>
         <v>872972099.9999994</v>
       </c>
-      <c r="D145" t="str">
+      <c r="D149" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E145" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" cm="1">
-        <f t="array" ref="A146">MULTINOMIAL({1;2},3,4)</f>
+      <c r="E149" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" cm="1">
+        <f t="array" ref="A150">MULTINOMIAL({1;2},3,4)</f>
         <v>12599.999999999995</v>
       </c>
-      <c r="B146">
+      <c r="B150">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C146">
+      <c r="C150">
         <f t="shared" si="7"/>
         <v>12599.999999999995</v>
       </c>
-      <c r="D146" t="str">
+      <c r="D150" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E146" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" cm="1">
-        <f t="array" ref="A147">MULTINOMIAL(2,D!B1:B2,4)</f>
+      <c r="E150" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" cm="1">
+        <f t="array" ref="A151">MULTINOMIAL(2,D!B1:B2,4)</f>
         <v>137837700.00000036</v>
       </c>
-      <c r="B147">
+      <c r="B151">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C147">
+      <c r="C151">
         <f t="shared" si="7"/>
         <v>137837700.00000036</v>
       </c>
-      <c r="D147" t="str">
+      <c r="D151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E147" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" cm="1">
-        <f t="array" ref="A148">MULTINOMIAL(2,{1;2},4)</f>
+      <c r="E151" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" cm="1">
+        <f t="array" ref="A152">MULTINOMIAL(2,{1;2},4)</f>
         <v>3779.9999999999986</v>
       </c>
-      <c r="B148">
+      <c r="B152">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C148">
+      <c r="C152">
         <f t="shared" si="7"/>
         <v>3779.9999999999986</v>
       </c>
-      <c r="D148" t="str">
+      <c r="D152" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E148" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" cm="1">
-        <f t="array" ref="A149">MULTINOMIAL(2,3,D!B1:B2)</f>
+      <c r="E152" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" cm="1">
+        <f t="array" ref="A153">MULTINOMIAL(2,3,D!B1:B2)</f>
         <v>30630600.00000006</v>
       </c>
-      <c r="B149">
+      <c r="B153">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C149">
+      <c r="C153">
         <f t="shared" si="7"/>
         <v>30630600.00000006</v>
       </c>
-      <c r="D149" t="str">
+      <c r="D153" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E149" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" cm="1">
-        <f t="array" ref="A150">MULTINOMIAL(2,3,{1;2})</f>
+      <c r="E153" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" cm="1">
+        <f t="array" ref="A154">MULTINOMIAL(2,3,{1;2})</f>
         <v>1680</v>
       </c>
-      <c r="B150">
+      <c r="B154">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C150">
+      <c r="C154">
         <f t="shared" si="7"/>
         <v>1680</v>
       </c>
-      <c r="D150" t="str">
+      <c r="D154" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="E150" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" cm="1">
-        <f t="array" ref="A151">N(D!B1:B2)</f>
+      <c r="E154" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" cm="1">
+        <f t="array" ref="A155">N(D!B1:B2)</f>
         <v>4</v>
       </c>
-      <c r="B151">
+      <c r="B155">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C151">
+      <c r="C155">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="D151" t="str">
+      <c r="D155" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="E151" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A152" ca="1">N({1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B152">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C152">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D152" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E152" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A153" ca="1">_xlfn.NEGBINOM.DIST(D!B1:B2,5,0.25,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B153">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C153">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D153" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E153" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A154" ca="1">_xlfn.NEGBINOM.DIST({1;2},5,0.25,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B154">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C154">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D154" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="E154" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A155" ca="1">_xlfn.NEGBINOM.DIST(10,D!B1:B2,0.25,TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B155">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="C155">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="D155" t="str">
-        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E155" t="s">
@@ -6302,7 +6302,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A156" ca="1">_xlfn.NEGBINOM.DIST(10,{1;2},0.25,TRUE)</f>
+        <f t="array" aca="1" ref="A156" ca="1">N({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B156">
@@ -6323,7 +6323,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A157" ca="1">_xlfn.NEGBINOM.DIST(10,5,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A157" ca="1">_xlfn.NEGBINOM.DIST(D!B1:B2,5,0.25,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B157">
@@ -6344,7 +6344,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A158" ca="1">_xlfn.NEGBINOM.DIST(10,5,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A158" ca="1">_xlfn.NEGBINOM.DIST({1;2},5,0.25,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B158">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A159" ca="1">_xlfn.NEGBINOM.DIST(10,5,0.25,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A159" ca="1">_xlfn.NEGBINOM.DIST(10,D!B1:B2,0.25,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B159">
@@ -6386,7 +6386,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A160" ca="1">_xlfn.NEGBINOM.DIST(10,5,0.25,{1;2})</f>
+        <f t="array" aca="1" ref="A160" ca="1">_xlfn.NEGBINOM.DIST(10,{1;2},0.25,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B160">
@@ -6407,7 +6407,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A161" ca="1">NEGBINOMDIST(D!B1:B2,5,0.25)</f>
+        <f t="array" aca="1" ref="A161" ca="1">_xlfn.NEGBINOM.DIST(10,5,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B161">
@@ -6428,7 +6428,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A162" ca="1">NEGBINOMDIST({1;2},5,0.25)</f>
+        <f t="array" aca="1" ref="A162" ca="1">_xlfn.NEGBINOM.DIST(10,5,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B162">
@@ -6449,7 +6449,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A163" ca="1">NEGBINOMDIST(10,D!B1:B2,0.25)</f>
+        <f t="array" aca="1" ref="A163" ca="1">_xlfn.NEGBINOM.DIST(10,5,0.25,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B163">
@@ -6470,7 +6470,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A164" ca="1">NEGBINOMDIST(10,{1;2},0.25)</f>
+        <f t="array" aca="1" ref="A164" ca="1">_xlfn.NEGBINOM.DIST(10,5,0.25,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B164">
@@ -6491,7 +6491,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A165" ca="1">NEGBINOMDIST(10,5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A165" ca="1">NEGBINOMDIST(D!B1:B2,5,0.25)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B165">
@@ -6512,7 +6512,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A166" ca="1">NEGBINOMDIST(10,5,{1;2})</f>
+        <f t="array" aca="1" ref="A166" ca="1">NEGBINOMDIST({1;2},5,0.25)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B166">
@@ -6532,20 +6532,20 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" t="e" cm="1">
-        <f t="array" ref="A167">NETWORKDAYS(D!B1:B2,41334)</f>
+      <c r="A167" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A167" ca="1">NEGBINOMDIST(10,D!B1:B2,0.25)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B167">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C167">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="D167" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E167" t="s">
@@ -6554,7 +6554,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A168" ca="1">NETWORKDAYS({1;2},41334)</f>
+        <f t="array" aca="1" ref="A168" ca="1">NEGBINOMDIST(10,{1;2},0.25)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B168">
@@ -6574,20 +6574,20 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169" t="e" cm="1">
-        <f t="array" ref="A169">NETWORKDAYS(41183,D!B1:B2)</f>
+      <c r="A169" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A169" ca="1">NEGBINOMDIST(10,5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B169">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9</v>
       </c>
       <c r="C169">
-        <f t="shared" si="7"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="D169" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ca="1" si="8"/>
         <v/>
       </c>
       <c r="E169" t="s">
@@ -6596,7 +6596,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A170" ca="1">NETWORKDAYS(41183,{1;2})</f>
+        <f t="array" aca="1" ref="A170" ca="1">NEGBINOMDIST(10,5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B170">
@@ -6617,7 +6617,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="e" cm="1">
-        <f t="array" ref="A171">NETWORKDAYS.INTL(D!B1:B2,38748)</f>
+        <f t="array" ref="A171">NETWORKDAYS(D!B1:B2,41334)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B171">
@@ -6638,7 +6638,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A172" ca="1">NETWORKDAYS.INTL({1;2},38748)</f>
+        <f t="array" aca="1" ref="A172" ca="1">NETWORKDAYS({1;2},41334)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B172">
@@ -6659,7 +6659,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="e" cm="1">
-        <f t="array" ref="A173">NETWORKDAYS.INTL(38718,D!B1:B2)</f>
+        <f t="array" ref="A173">NETWORKDAYS(41183,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B173">
@@ -6680,7 +6680,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A174" ca="1">NETWORKDAYS.INTL(38718,{1;2})</f>
+        <f t="array" aca="1" ref="A174" ca="1">NETWORKDAYS(41183,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B174">
@@ -6701,7 +6701,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="e" cm="1">
-        <f t="array" ref="A175">NOMINAL(D!B1:B2,4)</f>
+        <f t="array" ref="A175">NETWORKDAYS.INTL(D!B1:B2,38748)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B175">
@@ -6722,7 +6722,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A176" ca="1">NOMINAL({1;2},4)</f>
+        <f t="array" aca="1" ref="A176" ca="1">NETWORKDAYS.INTL({1;2},38748)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B176">
@@ -6743,7 +6743,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="e" cm="1">
-        <f t="array" ref="A177">NOMINAL(0.053543,D!B1:B2)</f>
+        <f t="array" ref="A177">NETWORKDAYS.INTL(38718,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B177">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A178" ca="1">NOMINAL(0.053543,{1;2})</f>
+        <f t="array" aca="1" ref="A178" ca="1">NETWORKDAYS.INTL(38718,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B178">
@@ -6784,20 +6784,20 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A179" ca="1">_xlfn.NORM.DIST(D!B1:B2,40,1.5,TRUE)</f>
+      <c r="A179" t="e" cm="1">
+        <f t="array" ref="A179">NOMINAL(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B179">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="C179">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D179" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="E179" t="s">
@@ -6806,7 +6806,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A180" ca="1">_xlfn.NORM.DIST({1;2},40,1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A180" ca="1">NOMINAL({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B180">
@@ -6826,20 +6826,20 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A181" ca="1">_xlfn.NORM.DIST(42,D!B1:B2,1.5,TRUE)</f>
+      <c r="A181" t="e" cm="1">
+        <f t="array" ref="A181">NOMINAL(0.053543,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B181">
-        <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="C181">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D181" t="str">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="E181" t="s">
@@ -6848,7 +6848,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A182" ca="1">_xlfn.NORM.DIST(42,{1;2},1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A182" ca="1">NOMINAL(0.053543,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B182">
@@ -6869,7 +6869,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A183" ca="1">_xlfn.NORM.DIST(42,40,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A183" ca="1">_xlfn.NORM.DIST(D!B1:B2,40,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B183">
@@ -6890,7 +6890,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A184" ca="1">_xlfn.NORM.DIST(42,40,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A184" ca="1">_xlfn.NORM.DIST({1;2},40,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B184">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A185" ca="1">_xlfn.NORM.DIST(42,40,1.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A185" ca="1">_xlfn.NORM.DIST(42,D!B1:B2,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B185">
@@ -6932,7 +6932,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A186" ca="1">_xlfn.NORM.DIST(42,40,1.5,{1;2})</f>
+        <f t="array" aca="1" ref="A186" ca="1">_xlfn.NORM.DIST(42,{1;2},1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B186">
@@ -6953,7 +6953,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A187" ca="1">_xlfn.NORM.INV(D!B1:B2,40,1.5)</f>
+        <f t="array" aca="1" ref="A187" ca="1">_xlfn.NORM.DIST(42,40,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B187">
@@ -6974,7 +6974,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A188" ca="1">_xlfn.NORM.INV({1;2},40,1.5)</f>
+        <f t="array" aca="1" ref="A188" ca="1">_xlfn.NORM.DIST(42,40,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B188">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A189" ca="1">_xlfn.NORM.INV(0.908789,D!B1:B2,1.5)</f>
+        <f t="array" aca="1" ref="A189" ca="1">_xlfn.NORM.DIST(42,40,1.5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B189">
@@ -7016,7 +7016,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A190" ca="1">_xlfn.NORM.INV(0.908789,{1;2},1.5)</f>
+        <f t="array" aca="1" ref="A190" ca="1">_xlfn.NORM.DIST(42,40,1.5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B190">
@@ -7037,7 +7037,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A191" ca="1">_xlfn.NORM.INV(0.908789,40,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A191" ca="1">_xlfn.NORM.INV(D!B1:B2,40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B191">
@@ -7058,7 +7058,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A192" ca="1">_xlfn.NORM.INV(0.908789,40,{1;2})</f>
+        <f t="array" aca="1" ref="A192" ca="1">_xlfn.NORM.INV({1;2},40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B192">
@@ -7079,7 +7079,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A193" ca="1">_xlfn.NORM.S.DIST(D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A193" ca="1">_xlfn.NORM.INV(0.908789,D!B1:B2,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B193">
@@ -7100,7 +7100,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A194" ca="1">_xlfn.NORM.S.DIST({1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A194" ca="1">_xlfn.NORM.INV(0.908789,{1;2},1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B194">
@@ -7121,7 +7121,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A195" ca="1">_xlfn.NORM.S.DIST(1.333333,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A195" ca="1">_xlfn.NORM.INV(0.908789,40,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B195">
@@ -7142,7 +7142,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A196" ca="1">_xlfn.NORM.S.DIST(1.333333,{1;2})</f>
+        <f t="array" aca="1" ref="A196" ca="1">_xlfn.NORM.INV(0.908789,40,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B196">
@@ -7163,7 +7163,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A197" ca="1">_xlfn.NORM.S.INV(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A197" ca="1">_xlfn.NORM.S.DIST(D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B197">
@@ -7184,7 +7184,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A198" ca="1">_xlfn.NORM.S.INV({1;2})</f>
+        <f t="array" aca="1" ref="A198" ca="1">_xlfn.NORM.S.DIST({1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B198">
@@ -7205,7 +7205,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A199" ca="1">NORMDIST(D!B1:B2,40,1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A199" ca="1">_xlfn.NORM.S.DIST(1.333333,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B199">
@@ -7226,7 +7226,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A200" ca="1">NORMDIST({1;2},40,1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A200" ca="1">_xlfn.NORM.S.DIST(1.333333,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B200">
@@ -7247,7 +7247,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A201" ca="1">NORMDIST(42,D!B1:B2,1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A201" ca="1">_xlfn.NORM.S.INV(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B201">
@@ -7268,7 +7268,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A202" ca="1">NORMDIST(42,{1;2},1.5,TRUE)</f>
+        <f t="array" aca="1" ref="A202" ca="1">_xlfn.NORM.S.INV({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B202">
@@ -7289,7 +7289,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A203" ca="1">NORMDIST(42,40,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A203" ca="1">NORMDIST(D!B1:B2,40,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B203">
@@ -7310,7 +7310,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A204" ca="1">NORMDIST(42,40,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A204" ca="1">NORMDIST({1;2},40,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B204">
@@ -7331,7 +7331,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A205" ca="1">NORMDIST(42,40,1.5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A205" ca="1">NORMDIST(42,D!B1:B2,1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B205">
@@ -7352,7 +7352,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A206" ca="1">NORMDIST(42,40,1.5,{1;2})</f>
+        <f t="array" aca="1" ref="A206" ca="1">NORMDIST(42,{1;2},1.5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B206">
@@ -7373,7 +7373,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A207" ca="1">NORMINV(D!B1:B2,40,1.5)</f>
+        <f t="array" aca="1" ref="A207" ca="1">NORMDIST(42,40,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B207">
@@ -7394,7 +7394,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A208" ca="1">NORMINV({1;2},40,1.5)</f>
+        <f t="array" aca="1" ref="A208" ca="1">NORMDIST(42,40,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B208">
@@ -7415,7 +7415,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A209" ca="1">NORMINV(0.908789,D!B1:B2,1.5)</f>
+        <f t="array" aca="1" ref="A209" ca="1">NORMDIST(42,40,1.5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B209">
@@ -7436,7 +7436,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A210" ca="1">NORMINV(0.908789,{1;2},1.5)</f>
+        <f t="array" aca="1" ref="A210" ca="1">NORMDIST(42,40,1.5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B210">
@@ -7457,7 +7457,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A211" ca="1">NORMINV(0.908789,40,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A211" ca="1">NORMINV(D!B1:B2,40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B211">
@@ -7478,7 +7478,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A212" ca="1">NORMINV(0.908789,40,{1;2})</f>
+        <f t="array" aca="1" ref="A212" ca="1">NORMINV({1;2},40,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B212">
@@ -7499,7 +7499,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A213" ca="1">NORMSDIST(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A213" ca="1">NORMINV(0.908789,D!B1:B2,1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B213">
@@ -7520,7 +7520,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A214" ca="1">NORMSDIST({1;2})</f>
+        <f t="array" aca="1" ref="A214" ca="1">NORMINV(0.908789,{1;2},1.5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B214">
@@ -7541,7 +7541,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A215" ca="1">NORMSINV(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A215" ca="1">NORMINV(0.908789,40,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B215">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A216" ca="1">NORMSINV({1;2})</f>
+        <f t="array" aca="1" ref="A216" ca="1">NORMINV(0.908789,40,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B216">
@@ -7583,7 +7583,7 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A217" ca="1">NOT(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A217" ca="1">NORMSDIST(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B217">
@@ -7604,7 +7604,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A218" ca="1">NOT({1;2})</f>
+        <f t="array" aca="1" ref="A218" ca="1">NORMSDIST({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B218">
@@ -7625,7 +7625,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A219" ca="1">NPER(D!B1:B2,-100,-1000,10000,1)</f>
+        <f t="array" aca="1" ref="A219" ca="1">NORMSINV(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B219">
@@ -7646,7 +7646,7 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A220" ca="1">NPER({1;2},-100,-1000,10000,1)</f>
+        <f t="array" aca="1" ref="A220" ca="1">NORMSINV({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B220">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A221" ca="1">NPER(0.01,D!B1:B2,-1000,10000,1)</f>
+        <f t="array" aca="1" ref="A221" ca="1">NOT(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B221">
@@ -7688,7 +7688,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A222" ca="1">NPER(0.01,{1;2},-1000,10000,1)</f>
+        <f t="array" aca="1" ref="A222" ca="1">NOT({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B222">
@@ -7709,7 +7709,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A223" ca="1">NPER(0.01,-100,D!B1:B2,10000,1)</f>
+        <f t="array" aca="1" ref="A223" ca="1">NPER(D!B1:B2,-100,-1000,10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B223">
@@ -7730,7 +7730,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A224" ca="1">NPER(0.01,-100,{1;2},10000,1)</f>
+        <f t="array" aca="1" ref="A224" ca="1">NPER({1;2},-100,-1000,10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B224">
@@ -7751,7 +7751,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A225" ca="1">NPER(0.01,-100,-1000,D!B1:B2,1)</f>
+        <f t="array" aca="1" ref="A225" ca="1">NPER(0.01,D!B1:B2,-1000,10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B225">
@@ -7772,7 +7772,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A226" ca="1">NPER(0.01,-100,-1000,{1;2},1)</f>
+        <f t="array" aca="1" ref="A226" ca="1">NPER(0.01,{1;2},-1000,10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B226">
@@ -7793,7 +7793,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A227" ca="1">NPER(0.01,-100,-1000,10000,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A227" ca="1">NPER(0.01,-100,D!B1:B2,10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B227">
@@ -7814,7 +7814,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A228" ca="1">NPER(0.01,-100,-1000,10000,{1;2})</f>
+        <f t="array" aca="1" ref="A228" ca="1">NPER(0.01,-100,{1;2},10000,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B228">
@@ -7835,7 +7835,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A229" ca="1">NPV(D!B1:B2,-10000,3000,4200,6800)</f>
+        <f t="array" aca="1" ref="A229" ca="1">NPER(0.01,-100,-1000,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B229">
@@ -7856,7 +7856,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A230" ca="1">NPV({1;2},-10000,3000,4200,6800)</f>
+        <f t="array" aca="1" ref="A230" ca="1">NPER(0.01,-100,-1000,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B230">
@@ -7876,251 +7876,251 @@
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A231" cm="1">
-        <f t="array" ref="A231">NPV(0.1,D!B1:B2,3000,4200,6800)</f>
+      <c r="A231" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A231" ca="1">NPER(0.01,-100,-1000,10000,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B231">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C231">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D231" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E231" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A232" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A232" ca="1">NPER(0.01,-100,-1000,10000,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B232">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C232">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D232" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E232" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A233" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A233" ca="1">NPV(D!B1:B2,-10000,3000,4200,6800)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B233">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C233">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D233" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E233" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A234" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A234" ca="1">NPV({1;2},-10000,3000,4200,6800)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B234">
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="C234">
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="D234" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="E234" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A235" cm="1">
+        <f t="array" ref="A235">NPV(0.1,D!B1:B2,3000,4200,6800)</f>
         <v>9355.1138459245794</v>
       </c>
-      <c r="B231">
+      <c r="B235">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C231">
+      <c r="C235">
         <f t="shared" si="10"/>
         <v>9355.1138459245794</v>
       </c>
-      <c r="D231" t="str">
+      <c r="D235" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E231" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A232" cm="1">
-        <f t="array" ref="A232">NPV(0.1,{1;2},3000,4200,6800)</f>
+      <c r="E235" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A236" cm="1">
+        <f t="array" ref="A236">NPV(0.1,{1;2},3000,4200,6800)</f>
         <v>9347.427895511355</v>
       </c>
-      <c r="B232">
+      <c r="B236">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C232">
+      <c r="C236">
         <f t="shared" si="10"/>
         <v>9347.427895511355</v>
       </c>
-      <c r="D232" t="str">
+      <c r="D236" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E232" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A233" cm="1">
-        <f t="array" ref="A233">NPV(0.1,-10000,D!B1:B2,4200,6800)</f>
+      <c r="E236" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A237" cm="1">
+        <f t="array" ref="A237">NPV(0.1,-10000,D!B1:B2,4200,6800)</f>
         <v>-1990.6712780423613</v>
       </c>
-      <c r="B233">
+      <c r="B237">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C233">
+      <c r="C237">
         <f t="shared" si="10"/>
         <v>-1990.6712780423613</v>
       </c>
-      <c r="D233" t="str">
+      <c r="D237" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E233" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A234" cm="1">
-        <f t="array" ref="A234">NPV(0.1,-10000,{1;2},4200,6800)</f>
+      <c r="E237" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A238" cm="1">
+        <f t="array" ref="A238">NPV(0.1,-10000,{1;2},4200,6800)</f>
         <v>-1997.6585056907472</v>
       </c>
-      <c r="B234">
+      <c r="B238">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C234">
+      <c r="C238">
         <f t="shared" si="10"/>
         <v>-1997.6585056907472</v>
       </c>
-      <c r="D234" t="str">
+      <c r="D238" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E234" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A235" cm="1">
-        <f t="array" ref="A235">NPV(0.1,-10000,3000,D!B1:B2,6800)</f>
+      <c r="E238" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A239" cm="1">
+        <f t="array" ref="A239">NPV(0.1,-10000,3000,D!B1:B2,6800)</f>
         <v>-2380.8358842851039</v>
       </c>
-      <c r="B235">
+      <c r="B239">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C235">
+      <c r="C239">
         <f t="shared" si="10"/>
         <v>-2380.8358842851039</v>
       </c>
-      <c r="D235" t="str">
+      <c r="D239" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E235" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A236" cm="1">
-        <f t="array" ref="A236">NPV(0.1,-10000,3000,{1;2},6800)</f>
+      <c r="E239" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A240" cm="1">
+        <f t="array" ref="A240">NPV(0.1,-10000,3000,{1;2},6800)</f>
         <v>-2387.1879094199994</v>
       </c>
-      <c r="B236">
+      <c r="B240">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C236">
+      <c r="C240">
         <f t="shared" si="10"/>
         <v>-2387.1879094199994</v>
       </c>
-      <c r="D236" t="str">
+      <c r="D240" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E236" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A237" cm="1">
-        <f t="array" ref="A237">NPV(0.1,-10000,3000,4200,D!B1:B2)</f>
+      <c r="E240" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241" cm="1">
+        <f t="array" ref="A241">NPV(0.1,-10000,3000,4200,D!B1:B2)</f>
         <v>-3448.3486597413244</v>
       </c>
-      <c r="B237">
+      <c r="B241">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C237">
+      <c r="C241">
         <f t="shared" si="10"/>
         <v>-3448.3486597413244</v>
       </c>
-      <c r="D237" t="str">
+      <c r="D241" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="E237" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238" cm="1">
-        <f t="array" ref="A238">NPV(0.1,-10000,3000,4200,{1;2})</f>
+      <c r="E241" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A242" cm="1">
+        <f t="array" ref="A242">NPV(0.1,-10000,3000,4200,{1;2})</f>
         <v>-3454.1232280457748</v>
       </c>
-      <c r="B238">
+      <c r="B242">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="C238">
+      <c r="C242">
         <f t="shared" si="10"/>
         <v>-3454.1232280457748</v>
       </c>
-      <c r="D238" t="str">
+      <c r="D242" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="E238" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A239" ca="1">_xlfn.NUMBERVALUE(D!B1:B2,",",".")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B239">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C239">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D239" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E239" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A240" ca="1">_xlfn.NUMBERVALUE({1;2},",",".")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B240">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C240">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D240" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E240" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A241" ca="1">_xlfn.NUMBERVALUE("2.500,27",D!B1:B2,".")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B241">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C241">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D241" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="E241" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A242" ca="1">_xlfn.NUMBERVALUE("2.500,27",{1;2},".")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B242">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="C242">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="D242" t="str">
-        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E242" t="s">
@@ -8129,7 +8129,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A243" ca="1">_xlfn.NUMBERVALUE("2.500,27",",",D!B1:B2)</f>
+        <f t="array" aca="1" ref="A243" ca="1">_xlfn.NUMBERVALUE(D!B1:B2,",",".")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B243">
@@ -8150,7 +8150,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A244" ca="1">_xlfn.NUMBERVALUE("2.500,27",",",{1;2})</f>
+        <f t="array" aca="1" ref="A244" ca="1">_xlfn.NUMBERVALUE({1;2},",",".")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B244">
@@ -8170,20 +8170,20 @@
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" t="e" cm="1">
-        <f t="array" ref="A245">OCT2BIN(D!B1:B2,3)</f>
+      <c r="A245" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A245" ca="1">_xlfn.NUMBERVALUE("2.500,27",D!B1:B2,".")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B245">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
       </c>
       <c r="C245">
-        <f t="shared" si="10"/>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E245" t="s">
@@ -8192,7 +8192,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A246" ca="1">OCT2BIN({1;2},3)</f>
+        <f t="array" aca="1" ref="A246" ca="1">_xlfn.NUMBERVALUE("2.500,27",{1;2},".")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B246">
@@ -8212,20 +8212,20 @@
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" t="e" cm="1">
-        <f t="array" ref="A247">OCT2BIN("3",D!B1:B2)</f>
+      <c r="A247" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A247" ca="1">_xlfn.NUMBERVALUE("2.500,27",",",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B247">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>9</v>
       </c>
       <c r="C247">
-        <f t="shared" si="10"/>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="D247" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
       <c r="E247" t="s">
@@ -8234,7 +8234,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A248" ca="1">OCT2BIN("3",{1;2})</f>
+        <f t="array" aca="1" ref="A248" ca="1">_xlfn.NUMBERVALUE("2.500,27",",",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B248">
@@ -8255,7 +8255,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="e" cm="1">
-        <f t="array" ref="A249">OCT2DEC(D!B1:B2)</f>
+        <f t="array" ref="A249">OCT2BIN(D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B249">
@@ -8276,7 +8276,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A250" ca="1">OCT2DEC({1;2})</f>
+        <f t="array" aca="1" ref="A250" ca="1">OCT2BIN({1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B250">
@@ -8297,7 +8297,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="e" cm="1">
-        <f t="array" ref="A251">OCT2HEX(D!B1:B2,4)</f>
+        <f t="array" ref="A251">OCT2BIN("3",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B251">
@@ -8318,7 +8318,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A252" ca="1">OCT2HEX({1;2},4)</f>
+        <f t="array" aca="1" ref="A252" ca="1">OCT2BIN("3",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B252">
@@ -8339,7 +8339,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="e" cm="1">
-        <f t="array" ref="A253">OCT2HEX("100",D!B1:B2)</f>
+        <f t="array" ref="A253">OCT2DEC(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B253">
@@ -8360,7 +8360,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A254" ca="1">OCT2HEX("100",{1;2})</f>
+        <f t="array" aca="1" ref="A254" ca="1">OCT2DEC({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B254">
@@ -8380,20 +8380,20 @@
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A255" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A255" ca="1">ODD(D!B1:B2)</f>
+      <c r="A255" t="e" cm="1">
+        <f t="array" ref="A255">OCT2HEX(D!B1:B2,4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B255">
-        <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="C255">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D255" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E255" t="s">
@@ -8402,7 +8402,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A256" ca="1">ODD({1;2})</f>
+        <f t="array" aca="1" ref="A256" ca="1">OCT2HEX({1;2},4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B256">
@@ -8423,7 +8423,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" t="e" cm="1">
-        <f t="array" ref="A257">ODDFPRICE(D!B1:B2,DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <f t="array" ref="A257">OCT2HEX("100",D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B257">
@@ -8444,7 +8444,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A258" ca="1">ODDFPRICE({1;2},DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <f t="array" aca="1" ref="A258" ca="1">OCT2HEX("100",{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B258">
@@ -8464,20 +8464,20 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A259" t="e" cm="1">
-        <f t="array" ref="A259">ODDFPRICE(DATE(2008,11,11),D!B1:B2,DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+      <c r="A259" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A259" ca="1">ODD(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B259">
-        <f t="shared" si="12"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>9</v>
       </c>
       <c r="C259">
-        <f t="shared" si="13"/>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="D259" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
       <c r="E259" t="s">
@@ -8486,7 +8486,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A260" ca="1">ODDFPRICE(DATE(2008,11,11),{1;2},DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <f t="array" aca="1" ref="A260" ca="1">ODD({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B260">
@@ -8507,7 +8507,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="e" cm="1">
-        <f t="array" ref="A261">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),D!B1:B2,DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <f t="array" ref="A261">ODDFPRICE(D!B1:B2,DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B261">
@@ -8528,7 +8528,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A262" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),{1;2},DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
+        <f t="array" aca="1" ref="A262" ca="1">ODDFPRICE({1;2},DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B262">
@@ -8549,7 +8549,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="e" cm="1">
-        <f t="array" ref="A263">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),D!B1:B2,0.0785,0.0625,100,2,1)</f>
+        <f t="array" ref="A263">ODDFPRICE(DATE(2008,11,11),D!B1:B2,DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B263">
@@ -8570,7 +8570,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A264" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),{1;2},0.0785,0.0625,100,2,1)</f>
+        <f t="array" aca="1" ref="A264" ca="1">ODDFPRICE(DATE(2008,11,11),{1;2},DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B264">
@@ -8591,7 +8591,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="e" cm="1">
-        <f t="array" ref="A265">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),D!B1:B2,0.0625,100,2,1)</f>
+        <f t="array" ref="A265">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),D!B1:B2,DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B265">
@@ -8612,7 +8612,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A266" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),{1;2},0.0625,100,2,1)</f>
+        <f t="array" aca="1" ref="A266" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),{1;2},DATE(2009,3,1),0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B266">
@@ -8633,7 +8633,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="e" cm="1">
-        <f t="array" ref="A267">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,D!B1:B2,100,2,1)</f>
+        <f t="array" ref="A267">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),D!B1:B2,0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B267">
@@ -8654,7 +8654,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A268" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,{1;2},100,2,1)</f>
+        <f t="array" aca="1" ref="A268" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),{1;2},0.0785,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B268">
@@ -8675,7 +8675,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" t="e" cm="1">
-        <f t="array" ref="A269">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,D!B1:B2,2,1)</f>
+        <f t="array" ref="A269">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),D!B1:B2,0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B269">
@@ -8696,7 +8696,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A270" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,{1;2},2,1)</f>
+        <f t="array" aca="1" ref="A270" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),{1;2},0.0625,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B270">
@@ -8717,7 +8717,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="e" cm="1">
-        <f t="array" ref="A271">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,D!B1:B2,1)</f>
+        <f t="array" ref="A271">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,D!B1:B2,100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B271">
@@ -8738,7 +8738,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A272" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,{1;2},1)</f>
+        <f t="array" aca="1" ref="A272" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,{1;2},100,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B272">
@@ -8759,7 +8759,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="e" cm="1">
-        <f t="array" ref="A273">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,D!B1:B2)</f>
+        <f t="array" ref="A273">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,D!B1:B2,2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B273">
@@ -8780,7 +8780,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A274" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A274" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,{1;2},2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B274">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" t="e" cm="1">
-        <f t="array" ref="A275">ODDFYIELD(D!B1:B2,DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" ref="A275">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,D!B1:B2,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B275">
@@ -8822,7 +8822,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A276" ca="1">ODDFYIELD({1;2},DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" aca="1" ref="A276" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,{1;2},1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B276">
@@ -8843,7 +8843,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" t="e" cm="1">
-        <f t="array" ref="A277">ODDFYIELD(DATE(2008,11,11),D!B1:B2,DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" ref="A277">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B277">
@@ -8864,7 +8864,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A278" ca="1">ODDFYIELD(DATE(2008,11,11),{1;2},DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" aca="1" ref="A278" ca="1">ODDFPRICE(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0785,0.0625,100,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B278">
@@ -8885,7 +8885,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="e" cm="1">
-        <f t="array" ref="A279">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),D!B1:B2,DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" ref="A279">ODDFYIELD(D!B1:B2,DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B279">
@@ -8906,7 +8906,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A280" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),{1;2},DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
+        <f t="array" aca="1" ref="A280" ca="1">ODDFYIELD({1;2},DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B280">
@@ -8927,7 +8927,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" t="e" cm="1">
-        <f t="array" ref="A281">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),D!B1:B2,0.0575,84.5,100,2,0)</f>
+        <f t="array" ref="A281">ODDFYIELD(DATE(2008,11,11),D!B1:B2,DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B281">
@@ -8948,7 +8948,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A282" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),{1;2},0.0575,84.5,100,2,0)</f>
+        <f t="array" aca="1" ref="A282" ca="1">ODDFYIELD(DATE(2008,11,11),{1;2},DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B282">
@@ -8969,7 +8969,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="e" cm="1">
-        <f t="array" ref="A283">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),D!B1:B2,84.5,100,2,0)</f>
+        <f t="array" ref="A283">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),D!B1:B2,DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B283">
@@ -8990,7 +8990,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A284" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),{1;2},84.5,100,2,0)</f>
+        <f t="array" aca="1" ref="A284" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),{1;2},DATE(2009,3,1),0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B284">
@@ -9011,7 +9011,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="e" cm="1">
-        <f t="array" ref="A285">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,D!B1:B2,100,2,0)</f>
+        <f t="array" ref="A285">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),D!B1:B2,0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B285">
@@ -9032,7 +9032,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A286" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,{1;2},100,2,0)</f>
+        <f t="array" aca="1" ref="A286" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),{1;2},0.0575,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B286">
@@ -9053,7 +9053,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" t="e" cm="1">
-        <f t="array" ref="A287">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,D!B1:B2,2,0)</f>
+        <f t="array" ref="A287">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),D!B1:B2,84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B287">
@@ -9074,7 +9074,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A288" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,{1;2},2,0)</f>
+        <f t="array" aca="1" ref="A288" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),{1;2},84.5,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B288">
@@ -9095,7 +9095,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="e" cm="1">
-        <f t="array" ref="A289">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,D!B1:B2,0)</f>
+        <f t="array" ref="A289">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,D!B1:B2,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B289">
@@ -9116,7 +9116,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A290" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,{1;2},0)</f>
+        <f t="array" aca="1" ref="A290" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,{1;2},100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B290">
@@ -9137,7 +9137,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="e" cm="1">
-        <f t="array" ref="A291">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,D!B1:B2)</f>
+        <f t="array" ref="A291">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,D!B1:B2,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B291">
@@ -9158,7 +9158,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A292" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A292" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,{1;2},2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B292">
@@ -9179,7 +9179,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="e" cm="1">
-        <f t="array" ref="A293">ODDLPRICE(D!B1:B2,DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
+        <f t="array" ref="A293">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B293">
@@ -9200,7 +9200,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A294" ca="1">ODDLPRICE({1;2},DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
+        <f t="array" aca="1" ref="A294" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B294">
@@ -9221,7 +9221,7 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="e" cm="1">
-        <f t="array" ref="A295">ODDLPRICE(DATE(2008,2,7),D!B1:B2,DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
+        <f t="array" ref="A295">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B295">
@@ -9242,7 +9242,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A296" ca="1">ODDLPRICE(DATE(2008,2,7),{1;2},DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
+        <f t="array" aca="1" ref="A296" ca="1">ODDFYIELD(DATE(2008,11,11),DATE(2021,3,1),DATE(2008,10,15),DATE(2009,3,1),0.0575,84.5,100,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B296">
@@ -9263,7 +9263,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="e" cm="1">
-        <f t="array" ref="A297">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),D!B1:B2,0.0375,0.0405,100,2,0)</f>
+        <f t="array" ref="A297">ODDLPRICE(D!B1:B2,DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B297">
@@ -9284,7 +9284,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A298" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),{1;2},0.0375,0.0405,100,2,0)</f>
+        <f t="array" aca="1" ref="A298" ca="1">ODDLPRICE({1;2},DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B298">
@@ -9305,7 +9305,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="e" cm="1">
-        <f t="array" ref="A299">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),D!B1:B2,0.0405,100,2,0)</f>
+        <f t="array" ref="A299">ODDLPRICE(DATE(2008,2,7),D!B1:B2,DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B299">
@@ -9326,7 +9326,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A300" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),{1;2},0.0405,100,2,0)</f>
+        <f t="array" aca="1" ref="A300" ca="1">ODDLPRICE(DATE(2008,2,7),{1;2},DATE(2007,10,15),0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B300">
@@ -9347,7 +9347,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="e" cm="1">
-        <f t="array" ref="A301">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,D!B1:B2,100,2,0)</f>
+        <f t="array" ref="A301">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),D!B1:B2,0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B301">
@@ -9368,7 +9368,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A302" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,{1;2},100,2,0)</f>
+        <f t="array" aca="1" ref="A302" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),{1;2},0.0375,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B302">
@@ -9389,7 +9389,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="e" cm="1">
-        <f t="array" ref="A303">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,D!B1:B2,2,0)</f>
+        <f t="array" ref="A303">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),D!B1:B2,0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B303">
@@ -9410,7 +9410,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A304" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,{1;2},2,0)</f>
+        <f t="array" aca="1" ref="A304" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),{1;2},0.0405,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B304">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" t="e" cm="1">
-        <f t="array" ref="A305">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,D!B1:B2,0)</f>
+        <f t="array" ref="A305">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,D!B1:B2,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B305">
@@ -9452,7 +9452,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A306" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,{1;2},0)</f>
+        <f t="array" aca="1" ref="A306" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,{1;2},100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B306">
@@ -9473,7 +9473,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="e" cm="1">
-        <f t="array" ref="A307">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,D!B1:B2)</f>
+        <f t="array" ref="A307">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,D!B1:B2,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B307">
@@ -9494,7 +9494,7 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A308" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A308" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,{1;2},2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B308">
@@ -9515,7 +9515,7 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="e" cm="1">
-        <f t="array" ref="A309">ODDLYIELD(D!B1:B2,DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
+        <f t="array" ref="A309">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B309">
@@ -9536,7 +9536,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A310" ca="1">ODDLYIELD({1;2},DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
+        <f t="array" aca="1" ref="A310" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B310">
@@ -9557,7 +9557,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="e" cm="1">
-        <f t="array" ref="A311">ODDLYIELD(DATE(2008,4,20),D!B1:B2,DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
+        <f t="array" ref="A311">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B311">
@@ -9578,7 +9578,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A312" ca="1">ODDLYIELD(DATE(2008,4,20),{1;2},DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
+        <f t="array" aca="1" ref="A312" ca="1">ODDLPRICE(DATE(2008,2,7),DATE(2008,6,15),DATE(2007,10,15),0.0375,0.0405,100,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B312">
@@ -9599,7 +9599,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="e" cm="1">
-        <f t="array" ref="A313">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),D!B1:B2,0.0375,99.875,100,2,0)</f>
+        <f t="array" ref="A313">ODDLYIELD(D!B1:B2,DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B313">
@@ -9620,7 +9620,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A314" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),{1;2},0.0375,99.875,100,2,0)</f>
+        <f t="array" aca="1" ref="A314" ca="1">ODDLYIELD({1;2},DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B314">
@@ -9641,7 +9641,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" t="e" cm="1">
-        <f t="array" ref="A315">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),D!B1:B2,99.875,100,2,0)</f>
+        <f t="array" ref="A315">ODDLYIELD(DATE(2008,4,20),D!B1:B2,DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B315">
@@ -9662,7 +9662,7 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A316" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),{1;2},99.875,100,2,0)</f>
+        <f t="array" aca="1" ref="A316" ca="1">ODDLYIELD(DATE(2008,4,20),{1;2},DATE(2007,12,24),0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B316">
@@ -9683,7 +9683,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" t="e" cm="1">
-        <f t="array" ref="A317">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,D!B1:B2,100,2,0)</f>
+        <f t="array" ref="A317">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),D!B1:B2,0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B317">
@@ -9704,7 +9704,7 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A318" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,{1;2},100,2,0)</f>
+        <f t="array" aca="1" ref="A318" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),{1;2},0.0375,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B318">
@@ -9725,7 +9725,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="e" cm="1">
-        <f t="array" ref="A319">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,D!B1:B2,2,0)</f>
+        <f t="array" ref="A319">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),D!B1:B2,99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B319">
@@ -9746,7 +9746,7 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A320" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,{1;2},2,0)</f>
+        <f t="array" aca="1" ref="A320" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),{1;2},99.875,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B320">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" t="e" cm="1">
-        <f t="array" ref="A321">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,D!B1:B2,0)</f>
+        <f t="array" ref="A321">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,D!B1:B2,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B321">
@@ -9788,7 +9788,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A322" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,{1;2},0)</f>
+        <f t="array" aca="1" ref="A322" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,{1;2},100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B322">
@@ -9809,7 +9809,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="e" cm="1">
-        <f t="array" ref="A323">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,D!B1:B2)</f>
+        <f t="array" ref="A323">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,D!B1:B2,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B323">
@@ -9830,7 +9830,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A324" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,{1;2})</f>
+        <f t="array" aca="1" ref="A324" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,{1;2},2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B324">
@@ -9850,13 +9850,13 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A325" t="b" cm="1">
-        <f t="array" ref="A325">OR(D!B1:B2,TRUE)</f>
-        <v>1</v>
+      <c r="A325" t="e" cm="1">
+        <f t="array" ref="A325">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,D!B1:B2,0)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B325">
         <f t="shared" si="15"/>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="C325">
         <f t="shared" si="16"/>
@@ -9871,125 +9871,125 @@
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A326" t="b" cm="1">
-        <f t="array" ref="A326">OR({1;2},TRUE)</f>
+      <c r="A326" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A326" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,{1;2},0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B326">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C326">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D326" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E326" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A327" t="e" cm="1">
+        <f t="array" ref="A327">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B327">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="C327">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D327" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="E327" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A328" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A328" ca="1">ODDLYIELD(DATE(2008,4,20),DATE(2008,6,15),DATE(2007,12,24),0.0375,99.875,100,2,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B328">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C328">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D328" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E328" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A329" t="b" cm="1">
+        <f t="array" ref="A329">OR(D!B1:B2,TRUE)</f>
         <v>1</v>
       </c>
-      <c r="B326">
+      <c r="B329">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="C326">
+      <c r="C329">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D326" t="str">
+      <c r="D329" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E326" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A327" t="b" cm="1">
-        <f t="array" ref="A327">OR(FALSE,D!B1:B2)</f>
+      <c r="E329" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A330" t="b" cm="1">
+        <f t="array" ref="A330">OR({1;2},TRUE)</f>
         <v>1</v>
       </c>
-      <c r="B327">
+      <c r="B330">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="C327">
+      <c r="C330">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D327" t="str">
+      <c r="D330" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E327" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A328" t="b" cm="1">
-        <f t="array" ref="A328">OR(FALSE,{1;2})</f>
+      <c r="E330" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A331" t="b" cm="1">
+        <f t="array" ref="A331">OR(FALSE,D!B1:B2)</f>
         <v>1</v>
       </c>
-      <c r="B328">
+      <c r="B331">
         <f t="shared" si="15"/>
         <v>-1</v>
       </c>
-      <c r="C328">
+      <c r="C331">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D328" t="str">
+      <c r="D331" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E328" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A329" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A329" ca="1">_xlfn.PDURATION(D!B1:B2,2000,2200)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B329">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C329">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D329" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E329" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A330" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A330" ca="1">_xlfn.PDURATION({1;2},2000,2200)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B330">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C330">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D330" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E330" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A331" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A331" ca="1">_xlfn.PDURATION(0.025,D!B1:B2,2200)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B331">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C331">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D331" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E331" t="s">
@@ -9997,20 +9997,20 @@
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A332" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A332" ca="1">_xlfn.PDURATION(0.025,{1;2},2200)</f>
-        <v>#VALUE!</v>
+      <c r="A332" t="b" cm="1">
+        <f t="array" ref="A332">OR(FALSE,{1;2})</f>
+        <v>1</v>
       </c>
       <c r="B332">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
+        <f t="shared" si="15"/>
+        <v>-1</v>
       </c>
       <c r="C332">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D332" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="E332" t="s">
@@ -10019,7 +10019,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A333" ca="1">_xlfn.PDURATION(0.025,2000,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A333" ca="1">_xlfn.PDURATION(D!B1:B2,2000,2200)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B333">
@@ -10040,7 +10040,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A334" ca="1">_xlfn.PDURATION(0.025,2000,{1;2})</f>
+        <f t="array" aca="1" ref="A334" ca="1">_xlfn.PDURATION({1;2},2000,2200)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B334">
@@ -10061,7 +10061,7 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A335" ca="1">PERCENTILE(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A335" ca="1">_xlfn.PDURATION(0.025,D!B1:B2,2200)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B335">
@@ -10082,7 +10082,7 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A336" ca="1">PERCENTILE(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A336" ca="1">_xlfn.PDURATION(0.025,{1;2},2200)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B336">
@@ -10103,7 +10103,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A337" ca="1">_xlfn.PERCENTILE.EXC(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A337" ca="1">_xlfn.PDURATION(0.025,2000,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B337">
@@ -10124,7 +10124,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A338" ca="1">_xlfn.PERCENTILE.EXC(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A338" ca="1">_xlfn.PDURATION(0.025,2000,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B338">
@@ -10145,7 +10145,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A339" ca="1">_xlfn.PERCENTILE.INC(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A339" ca="1">PERCENTILE(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B339">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A340" ca="1">_xlfn.PERCENTILE.INC(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A340" ca="1">PERCENTILE(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B340">
@@ -10186,167 +10186,167 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A341" cm="1">
-        <f t="array" ref="A341">_xlfn.PERCENTOF(D!B1:B2,4)</f>
+      <c r="A341" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A341" ca="1">_xlfn.PERCENTILE.EXC(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B341">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C341">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D341" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E341" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A342" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A342" ca="1">_xlfn.PERCENTILE.EXC(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B342">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C342">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D342" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E342" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A343" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A343" ca="1">_xlfn.PERCENTILE.INC(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B343">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C343">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D343" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E343" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A344" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A344" ca="1">_xlfn.PERCENTILE.INC(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B344">
+        <f t="shared" ca="1" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="C344">
+        <f t="shared" ca="1" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D344" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v/>
+      </c>
+      <c r="E344" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A345" cm="1">
+        <f t="array" ref="A345">_xlfn.PERCENTOF(D!B1:B2,4)</f>
         <v>3</v>
       </c>
-      <c r="B341">
+      <c r="B345">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C341">
+      <c r="C345">
         <f t="shared" si="16"/>
         <v>3</v>
       </c>
-      <c r="D341" t="str">
+      <c r="D345" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E341" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A342" cm="1">
-        <f t="array" ref="A342">_xlfn.PERCENTOF({1;2},4)</f>
+      <c r="E345" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A346" cm="1">
+        <f t="array" ref="A346">_xlfn.PERCENTOF({1;2},4)</f>
         <v>0.75</v>
       </c>
-      <c r="B342">
+      <c r="B346">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C342">
+      <c r="C346">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="D342" t="str">
+      <c r="D346" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E342" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A343" cm="1">
-        <f t="array" ref="A343">_xlfn.PERCENTOF(2,D!B1:B2)</f>
+      <c r="E346" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A347" cm="1">
+        <f t="array" ref="A347">_xlfn.PERCENTOF(2,D!B1:B2)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="B343">
+      <c r="B347">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C343">
+      <c r="C347">
         <f t="shared" si="16"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D343" t="str">
+      <c r="D347" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="E343" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A344" cm="1">
-        <f t="array" ref="A344">_xlfn.PERCENTOF(2,{1;2})</f>
+      <c r="E347" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A348" cm="1">
+        <f t="array" ref="A348">_xlfn.PERCENTOF(2,{1;2})</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="B344">
+      <c r="B348">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="C344">
+      <c r="C348">
         <f t="shared" si="16"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D344" t="str">
+      <c r="D348" t="str">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="E344" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A345" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A345" ca="1">PERCENTRANK(D!B1:B8,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B345">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C345">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D345" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E345" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A346" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A346" ca="1">PERCENTRANK(D!B1:B8,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B346">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C346">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D346" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E346" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A347" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A347" ca="1">_xlfn.PERCENTRANK.EXC(D!B1:B8,D!B1:B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B347">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C347">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D347" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-      <c r="E347" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A348" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A348" ca="1">_xlfn.PERCENTRANK.EXC(D!B1:B8,{1;2})</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B348">
-        <f t="shared" ca="1" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="C348">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D348" t="str">
-        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="E348" t="s">
@@ -10355,7 +10355,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A349" ca="1">_xlfn.PERCENTRANK.INC(D!B1:B8,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A349" ca="1">PERCENTRANK(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B349">
@@ -10376,7 +10376,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A350" ca="1">_xlfn.PERCENTRANK.INC(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A350" ca="1">PERCENTRANK(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B350">
@@ -10397,7 +10397,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A351" ca="1">PERMUT(D!B1:B2,3)</f>
+        <f t="array" aca="1" ref="A351" ca="1">_xlfn.PERCENTRANK.EXC(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B351">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A352" ca="1">PERMUT({1;2},3)</f>
+        <f t="array" aca="1" ref="A352" ca="1">_xlfn.PERCENTRANK.EXC(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B352">
@@ -10439,7 +10439,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A353" ca="1">PERMUT(100,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A353" ca="1">_xlfn.PERCENTRANK.INC(D!B1:B8,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B353">
@@ -10460,7 +10460,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A354" ca="1">PERMUT(100,{1;2})</f>
+        <f t="array" aca="1" ref="A354" ca="1">_xlfn.PERCENTRANK.INC(D!B1:B8,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B354">
@@ -10481,7 +10481,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A355" ca="1">_xlfn.PERMUTATIONA(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A355" ca="1">PERMUT(D!B1:B2,3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B355">
@@ -10502,7 +10502,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A356" ca="1">_xlfn.PERMUTATIONA({1;2},2)</f>
+        <f t="array" aca="1" ref="A356" ca="1">PERMUT({1;2},3)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B356">
@@ -10523,7 +10523,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A357" ca="1">_xlfn.PERMUTATIONA(3,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A357" ca="1">PERMUT(100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B357">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A358" ca="1">_xlfn.PERMUTATIONA(3,{1;2})</f>
+        <f t="array" aca="1" ref="A358" ca="1">PERMUT(100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B358">
@@ -10565,7 +10565,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A359" ca="1">_xlfn.PHI(D!B1:B2)</f>
+        <f t="array" aca="1" ref="A359" ca="1">_xlfn.PERMUTATIONA(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B359">
@@ -10586,7 +10586,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A360" ca="1">_xlfn.PHI({1;2})</f>
+        <f t="array" aca="1" ref="A360" ca="1">_xlfn.PERMUTATIONA({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B360">
@@ -10607,7 +10607,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A361" ca="1">PMT(D!B1:B2,10,10000)</f>
+        <f t="array" aca="1" ref="A361" ca="1">_xlfn.PERMUTATIONA(3,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B361">
@@ -10628,7 +10628,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A362" ca="1">PMT({1;2},10,10000)</f>
+        <f t="array" aca="1" ref="A362" ca="1">_xlfn.PERMUTATIONA(3,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B362">
@@ -10649,7 +10649,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A363" ca="1">PMT(0.00666666666666667,D!B1:B2,10000)</f>
+        <f t="array" aca="1" ref="A363" ca="1">_xlfn.PHI(D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B363">
@@ -10670,7 +10670,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A364" ca="1">PMT(0.00666666666666667,{1;2},10000)</f>
+        <f t="array" aca="1" ref="A364" ca="1">_xlfn.PHI({1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B364">
@@ -10691,7 +10691,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A365" ca="1">PMT(0.00666666666666667,10,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A365" ca="1">PMT(D!B1:B2,10,10000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B365">
@@ -10712,7 +10712,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A366" ca="1">PMT(0.00666666666666667,10,{1;2})</f>
+        <f t="array" aca="1" ref="A366" ca="1">PMT({1;2},10,10000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B366">
@@ -10733,7 +10733,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A367" ca="1">POISSON(D!B1:B2,5,TRUE)</f>
+        <f t="array" aca="1" ref="A367" ca="1">PMT(0.00666666666666667,D!B1:B2,10000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B367">
@@ -10754,7 +10754,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A368" ca="1">POISSON({1;2},5,TRUE)</f>
+        <f t="array" aca="1" ref="A368" ca="1">PMT(0.00666666666666667,{1;2},10000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B368">
@@ -10775,7 +10775,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A369" ca="1">POISSON(2,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A369" ca="1">PMT(0.00666666666666667,10,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B369">
@@ -10796,7 +10796,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A370" ca="1">POISSON(2,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A370" ca="1">PMT(0.00666666666666667,10,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B370">
@@ -10817,7 +10817,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A371" ca="1">POISSON(2,5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A371" ca="1">POISSON(D!B1:B2,5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B371">
@@ -10838,7 +10838,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A372" ca="1">POISSON(2,5,{1;2})</f>
+        <f t="array" aca="1" ref="A372" ca="1">POISSON({1;2},5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B372">
@@ -10859,7 +10859,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A373" ca="1">_xlfn.POISSON.DIST(D!B1:B2,5,TRUE)</f>
+        <f t="array" aca="1" ref="A373" ca="1">POISSON(2,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B373">
@@ -10880,7 +10880,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A374" ca="1">_xlfn.POISSON.DIST({1;2},5,TRUE)</f>
+        <f t="array" aca="1" ref="A374" ca="1">POISSON(2,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B374">
@@ -10901,7 +10901,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A375" ca="1">_xlfn.POISSON.DIST(2,D!B1:B2,TRUE)</f>
+        <f t="array" aca="1" ref="A375" ca="1">POISSON(2,5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B375">
@@ -10922,7 +10922,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A376" ca="1">_xlfn.POISSON.DIST(2,{1;2},TRUE)</f>
+        <f t="array" aca="1" ref="A376" ca="1">POISSON(2,5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B376">
@@ -10943,7 +10943,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A377" ca="1">_xlfn.POISSON.DIST(2,5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A377" ca="1">_xlfn.POISSON.DIST(D!B1:B2,5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B377">
@@ -10964,7 +10964,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A378" ca="1">_xlfn.POISSON.DIST(2,5,{1;2})</f>
+        <f t="array" aca="1" ref="A378" ca="1">_xlfn.POISSON.DIST({1;2},5,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B378">
@@ -10985,7 +10985,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A379" ca="1">POWER(D!B1:B2,2)</f>
+        <f t="array" aca="1" ref="A379" ca="1">_xlfn.POISSON.DIST(2,D!B1:B2,TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B379">
@@ -11006,7 +11006,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A380" ca="1">POWER({1;2},2)</f>
+        <f t="array" aca="1" ref="A380" ca="1">_xlfn.POISSON.DIST(2,{1;2},TRUE)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B380">
@@ -11027,7 +11027,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A381" ca="1">POWER(5,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A381" ca="1">_xlfn.POISSON.DIST(2,5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B381">
@@ -11048,7 +11048,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A382" ca="1">POWER(5,{1;2})</f>
+        <f t="array" aca="1" ref="A382" ca="1">_xlfn.POISSON.DIST(2,5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B382">
@@ -11069,7 +11069,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A383" ca="1">PPMT(D!B1:B2,1,24,2000)</f>
+        <f t="array" aca="1" ref="A383" ca="1">POWER(D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B383">
@@ -11090,7 +11090,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A384" ca="1">PPMT({1;2},1,24,2000)</f>
+        <f t="array" aca="1" ref="A384" ca="1">POWER({1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B384">
@@ -11111,7 +11111,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A385" ca="1">PPMT(0.00833333333333333,D!B1:B2,24,2000)</f>
+        <f t="array" aca="1" ref="A385" ca="1">POWER(5,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B385">
@@ -11132,7 +11132,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A386" ca="1">PPMT(0.00833333333333333,{1;2},24,2000)</f>
+        <f t="array" aca="1" ref="A386" ca="1">POWER(5,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B386">
@@ -11153,7 +11153,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A387" ca="1">PPMT(0.00833333333333333,1,D!B1:B2,2000)</f>
+        <f t="array" aca="1" ref="A387" ca="1">PPMT(D!B1:B2,1,24,2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B387">
@@ -11174,7 +11174,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A388" ca="1">PPMT(0.00833333333333333,1,{1;2},2000)</f>
+        <f t="array" aca="1" ref="A388" ca="1">PPMT({1;2},1,24,2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B388">
@@ -11195,7 +11195,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A389" ca="1">PPMT(0.00833333333333333,1,24,D!B1:B2)</f>
+        <f t="array" aca="1" ref="A389" ca="1">PPMT(0.00833333333333333,D!B1:B2,24,2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B389">
@@ -11216,7 +11216,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A390" ca="1">PPMT(0.00833333333333333,1,24,{1;2})</f>
+        <f t="array" aca="1" ref="A390" ca="1">PPMT(0.00833333333333333,{1;2},24,2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B390">
@@ -11236,20 +11236,20 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A391" t="e" cm="1">
-        <f t="array" ref="A391">PRICE(D!B1:B2,DATE(2017,11,15),0.0575,0.065,100,2,0)</f>
+      <c r="A391" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A391" ca="1">PPMT(0.00833333333333333,1,D!B1:B2,2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B391">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>9</v>
       </c>
       <c r="C391">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
       <c r="D391" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="E391" t="s">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A392" ca="1">PRICE({1;2},DATE(2017,11,15),0.0575,0.065,100,2,0)</f>
+        <f t="array" aca="1" ref="A392" ca="1">PPMT(0.00833333333333333,1,{1;2},2000)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B392">
@@ -11278,20 +11278,20 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A393" t="e" cm="1">
-        <f t="array" ref="A393">PRICE(DATE(2008,2,15),D!B1:B2,0.0575,0.065,100,2,0)</f>
+      <c r="A393" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A393" ca="1">PPMT(0.00833333333333333,1,24,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B393">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>9</v>
       </c>
       <c r="C393">
-        <f t="shared" si="19"/>
+        <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
       <c r="D393" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="E393" t="s">
@@ -11300,7 +11300,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A394" ca="1">PRICE(DATE(2008,2,15),{1;2},0.0575,0.065,100,2,0)</f>
+        <f t="array" aca="1" ref="A394" ca="1">PPMT(0.00833333333333333,1,24,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B394">
@@ -11321,7 +11321,7 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="e" cm="1">
-        <f t="array" ref="A395">PRICE(DATE(2008,2,15),DATE(2017,11,15),D!B1:B2,0.065,100,2,0)</f>
+        <f t="array" ref="A395">PRICE(D!B1:B2,DATE(2017,11,15),0.0575,0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B395">
@@ -11342,7 +11342,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A396" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),{1;2},0.065,100,2,0)</f>
+        <f t="array" aca="1" ref="A396" ca="1">PRICE({1;2},DATE(2017,11,15),0.0575,0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B396">
@@ -11363,7 +11363,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" t="e" cm="1">
-        <f t="array" ref="A397">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,D!B1:B2,100,2,0)</f>
+        <f t="array" ref="A397">PRICE(DATE(2008,2,15),D!B1:B2,0.0575,0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B397">
@@ -11384,7 +11384,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A398" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,{1;2},100,2,0)</f>
+        <f t="array" aca="1" ref="A398" ca="1">PRICE(DATE(2008,2,15),{1;2},0.0575,0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B398">
@@ -11405,7 +11405,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" t="e" cm="1">
-        <f t="array" ref="A399">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,D!B1:B2,2,0)</f>
+        <f t="array" ref="A399">PRICE(DATE(2008,2,15),DATE(2017,11,15),D!B1:B2,0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B399">
@@ -11426,7 +11426,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A400" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),0.0575,0.065,{1;2},2,0)</f>
+        <f t="array" aca="1" ref="A400" ca="1">PRICE(DATE(2008,2,15),DATE(2017,11,15),{1;2},0.065,100,2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B400">
